--- a/test-case-exports/W2WTransfer.xlsx
+++ b/test-case-exports/W2WTransfer.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Commission Management" automation (EMI-2031)</t>
+    <t>Skipped: pending Admin Portal "Commission Management" automation (EMI-2031)</t>
   </si>
   <si>
     <t>WT-CM02 — custom per-account schema overrides the default</t>
@@ -125,40 +125,100 @@
     <t>W2W Transfer — Verify Merchant &amp; Biller Balance Update</t>
   </si>
   <si>
-    <t>${data.testName} | Amount Type: ${data.amountType}</t>
+    <t>W2W_Transfer_Valid_Whole_Amount_Updates_Balances | Amount Type: Whole Number</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>dynamic title (template literal)</t>
+    <t>W2W_Transfer_Valid_Decimal_Amount_Updates_Balances | Amount Type: Decimal Amount</t>
   </si>
   <si>
     <t>W2W Transfer — Transaction Appears in Transaction Table</t>
   </si>
   <si>
-    <t>${data.testName}</t>
+    <t>W2W_Transfer_Transaction_Appears_In_Transaction_Table</t>
   </si>
   <si>
     <t>W2W Transfer — Invalid CRN Error Handling</t>
   </si>
   <si>
-    <t>${data.testName} | CRN Type: ${data.crnType}</t>
+    <t>W2W_Transfer_InvalidCRN_NonExistent | CRN Type: Non-Existent CRN</t>
+  </si>
+  <si>
+    <t>W2W_Transfer_InvalidCRN_IsSame_For_Sender_And_Receiver  | CRN Type: Self-Transfer CRN</t>
   </si>
   <si>
     <t>W2W Transfer — Amount Field Input Validation Layout</t>
   </si>
   <si>
-    <t>${data.testName} | Validation Type: ${data.amountValidation}</t>
+    <t>W2W_AmountValidation_Negative_Amount | Validation Type: Negative Amount</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Zero_Amount | Validation Type: Zero Amount</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Alphabetical_Characters | Validation Type: Alphabetical Characters</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Special_Characters | Validation Type: Special Characters</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Valid_Float_2_Decimals | Validation Type: Valid Float 2 Decimals</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Valid_Float_1_Decimal | Validation Type: Valid Float 1 Decimal</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Invalid_Float_3_Decimals | Validation Type: Invalid Float 3 Decimals</t>
+  </si>
+  <si>
+    <t>W2W_AmountValidation_Clipboard_Paste | Validation Type: Copy and Paste Amount Actions</t>
   </si>
   <si>
     <t>W2W Transfer — Insufficient Fund</t>
   </si>
   <si>
+    <t>W2W_Transfer_Insufficient_Fund</t>
+  </si>
+  <si>
     <t>W2W Transfer — CRN Field Input Validation Layout</t>
   </si>
   <si>
-    <t>${data.testName} | Validation Type: ${data.crnType}</t>
+    <t>W2W_Transfer_InvalidCRN_Empty | Validation Type: Empty CRN</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_LessThan_10_Digits | Validation Type: Less than 10 digits</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_Valid_10_to_15_Digits | Validation Type: Valid 10 to 15 digits</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_HardLimit_16_Digits | Validation Type: Exceeding 15 digits Hard Limit</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_Rejects_Alphabetic | Validation Type: Alphabetic characters</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_Rejects_SpecialChars | Validation Type: Special characters</t>
+  </si>
+  <si>
+    <t>W2W_CRN_Validation_Rejects_Spaces | Validation Type: Spaces in CRN</t>
+  </si>
+  <si>
+    <t>BusinessTestCases/W2WTransfer/functional/W2WTransferLocalization.spec.ts</t>
+  </si>
+  <si>
+    <t>W2WTransfer — Arabic Localization</t>
+  </si>
+  <si>
+    <t>should render the page in right-to-left direction</t>
+  </si>
+  <si>
+    <t>should resolve the CRN input and Check Recipient button via testid locators in Arabic</t>
+  </si>
+  <si>
+    <t>should display the Proceed button label in Arabic once the form is valid</t>
   </si>
   <si>
     <t>BusinessTestCases/W2WTransfer/functional/W2WTransferTransactionLimits.spec.ts</t>
@@ -170,7 +230,7 @@
     <t>WT-TL01 — transfers within the daily amount limit succeed (Web)</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Manage Limits → Transaction" automation (EMI-87/EMI-1653/EMI-195)</t>
+    <t>Skipped: pending Admin Portal "Manage Limits → Transaction" automation (EMI-87/EMI-1653/EMI-195)</t>
   </si>
   <si>
     <t>WT-TL02 — cumulative transfers exceeding the daily amount limit are blocked (Web)</t>
@@ -215,7 +275,7 @@
     <t>WT-WB01 — sender transfer within min-balance floor succeeds (Merchant, Low risk)</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Manage Limits → Wallet Balance" automation (EMI-1653/EMI-195)</t>
+    <t>Skipped: pending Admin Portal "Manage Limits → Wallet Balance" automation (EMI-1653/EMI-195)</t>
   </si>
   <si>
     <t>WT-WB02 — sender transfer breaching min-balance floor is blocked (Merchant, Low risk)</t>
@@ -245,13 +305,13 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.423Z</t>
+    <t>2026-09-08T15:08:53.889Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>functional</t>
@@ -263,7 +323,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -281,6 +344,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -290,7 +354,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,11 +364,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -322,8 +381,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -665,19 +728,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="57" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,36 +771,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -764,36 +829,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -822,36 +887,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -880,36 +945,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -938,36 +1003,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -996,36 +1061,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1054,36 +1119,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1112,36 +1177,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1170,36 +1235,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1228,36 +1293,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1271,10 +1336,10 @@
         <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>38</v>
@@ -1283,39 +1348,39 @@
         <v>15</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="E22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1329,10 +1394,10 @@
         <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>38</v>
@@ -1341,39 +1406,39 @@
         <v>15</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="E24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1387,10 +1452,10 @@
         <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>38</v>
@@ -1399,39 +1464,39 @@
         <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1439,57 +1504,57 @@
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1497,57 +1562,57 @@
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1555,57 +1620,57 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1613,57 +1678,57 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1671,57 +1736,57 @@
         <v>9</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1729,57 +1794,57 @@
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1787,57 +1852,57 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>69</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1854,48 +1919,48 @@
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>71</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1912,48 +1977,48 @@
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" t="s">
-        <v>73</v>
-      </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1961,29 +2026,551 @@
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>67</v>
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I63"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1991,60 +2578,91 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B4">
-        <v>44</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2057,18 +2675,34 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="4">
-        <v>4</v>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
